--- a/frontend/mobile/assets/bulk-import/TRU_Connect_Product_Import_Template.xlsx
+++ b/frontend/mobile/assets/bulk-import/TRU_Connect_Product_Import_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Categories" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Units" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +71,14 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +95,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00757575"/>
         <bgColor rgb="00757575"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E7D32"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00757575"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +152,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -499,9 +518,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -509,187 +528,417 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>compare_at_price</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>image_1</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>image_2</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>image_3</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>image_4</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>image_5</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Coca-Cola 500ml</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Beverages</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Each</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>SKU-000001</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Ice-cold 500ml bottle.</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>coke500.jpg</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>coke500_back.jpg</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="13" t="n"/>
+      <c r="L2" s="13" t="n"/>
+      <c r="M2" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Simba Chips 120g</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Snacks &amp; Confectionery</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Each</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="13" t="n"/>
+      <c r="H3" s="13" t="n"/>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>simba120.jpg</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+      <c r="J3" s="13" t="n"/>
+      <c r="K3" s="13" t="n"/>
+      <c r="L3" s="13" t="n"/>
+      <c r="M3" s="13" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Albany Bread</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Bakery</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>19.99</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>Each</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Delete the 3 rows above before uploading -- they're examples only. Green headers are required, grey are optional.</t>
-        </is>
-      </c>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Sliced white bread, 1 loaf per unit.</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="n"/>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="13" t="n"/>
+      <c r="K4" s="13" t="n"/>
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="13" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>How to fill in this template</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Required. The product's full name, e.g. "Coca-Cola 500ml".</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Required. Must exactly match one of the names on the Categories sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Required. Rands, e.g. 12.00 or 12,00 -- no currency symbol needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Required. What the price is for -- must exactly match one of the names on the Units sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Optional. How many you currently have. Leave blank to start at 0 (Out of stock until you add stock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Optional. Your own tracking label. Leave blank and TRU Connect generates one for you automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Optional. Plain text shown to businesses when they order, e.g. "3 loaves per case."</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>compare_at_price</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Optional. The "was" price for a sale, e.g. 25.00. Must be higher than price, or the row will show an error. Leave blank if you're not running a sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>image_1</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Optional. The exact filename of the main photo inside your images ZIP, e.g. "coke500.jpg".</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>image_2</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Optional. A second photo filename.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>image_3</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Optional. A third photo filename.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>image_4</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Optional. A fourth photo filename.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>image_5</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Optional. A fifth photo filename.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Images</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>If you're including photos, put them all in one ZIP file (no folders needed) and upload it alongside this spreadsheet. Each image_1 to image_5 value must exactly match a filename inside that ZIP, including the file extension (.jpg, .jpeg, .png, or .webp). Products without any image columns filled in will publish without a photo -- that's fine, you can add photos later.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -832,7 +1081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -945,172 +1194,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>How to fill in this template</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Required. The product's full name, e.g. "Coca-Cola 500ml".</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Required. Must exactly match one of the names on the Categories sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Required. Rands, e.g. 12.00 or 12,00 -- no currency symbol needed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Required. What the price is for -- must exactly match one of the names on the Units sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Optional. How many you currently have. Leave blank to start at 0 (Out of stock until you add stock).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>image_1</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Optional. The exact filename of the main photo inside your images ZIP, e.g. "coke500.jpg".</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>image_2</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Optional. A second photo filename.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>image_3</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Optional. A third photo filename.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>image_4</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Optional. A fourth photo filename.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>image_5</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Optional. A fifth photo filename.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Images</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>If you're including photos, put them all in one ZIP file (no folders needed) and upload it alongside this spreadsheet. Each image_1 to image_5 value must exactly match a filename inside that ZIP, including the file extension (.jpg, .jpeg, .png, or .webp). Products without any image columns filled in will publish without a photo -- that's fine, you can add photos later.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B18"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/frontend/mobile/assets/bulk-import/TRU_Connect_Product_Import_Template.xlsx
+++ b/frontend/mobile/assets/bulk-import/TRU_Connect_Product_Import_Template.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,56 +29,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C62828"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -87,28 +46,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E7D32"/>
-        <bgColor rgb="002E7D32"/>
+        <fgColor rgb="000B2545"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00757575"/>
-        <bgColor rgb="00757575"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E7D32"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00757575"/>
+        <fgColor rgb="001D4E89"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -116,45 +63,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,223 +445,255 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>compare_at_price</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>pack_quantity</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>pack_unit</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>image_1</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>image_2</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>image_3</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>image_4</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>image_5</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>Coca-Cola 500ml</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Coca-Cola Original 2L</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Beverages</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Each</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>SKU-000001</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
-        <is>
-          <t>Ice-cold 500ml bottle.</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>coke500.jpg</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
-        <is>
-          <t>coke500_back.jpg</t>
-        </is>
-      </c>
-      <c r="K2" s="13" t="n"/>
-      <c r="L2" s="13" t="n"/>
-      <c r="M2" s="13" t="n"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CC-2L</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2L PET bottle.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5449000054227</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>coke2l.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Simba Chips 120g</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Snacks &amp; Confectionery</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Iwisa Super Maize Meal 10kg</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Food &amp; Grocery</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>119.99</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>IW-10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Iwisa</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Albany White Bread 700g</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bakery</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>19.99</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Each</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="n"/>
-      <c r="G3" s="13" t="n"/>
-      <c r="H3" s="13" t="n"/>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>simba120.jpg</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="n"/>
-      <c r="K3" s="13" t="n"/>
-      <c r="L3" s="13" t="n"/>
-      <c r="M3" s="13" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Albany Bread</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Bakery</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Each</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="13" t="n"/>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Sliced white bread, 1 loaf per unit.</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="13" t="n"/>
-      <c r="L4" s="13" t="n"/>
-      <c r="M4" s="13" t="n"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sliced white, 1 loaf per unit.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -749,187 +706,341 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>How to fill in this template</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Required?</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Required. The product's full name, e.g. "Coca-Cola 500ml".</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>What the product is called.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Required. Must exactly match one of the names on the Categories sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>One of the TRU Connect categories, e.g. Beverages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Required. Rands, e.g. 12.00 or 12,00 -- no currency symbol needed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>What a business pays, in rands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Required. What the price is for -- must exactly match one of the names on the Units sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>How you sell it: Each, Case, Box, Bag...</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Optional. How many you currently have. Leave blank to start at 0 (Out of stock until you add stock).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>How many you have in stock right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Optional. Your own tracking label. Leave blank and TRU Connect generates one for you automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Your own product code. Include it and a re-uploaded price file UPDATES these products instead of adding duplicates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Optional. Plain text shown to businesses when they order, e.g. "3 loaves per case."</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Anything a business should know before ordering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>compare_at_price</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Optional. The "was" price for a sale, e.g. 25.00. Must be higher than price, or the row will show an error. Leave blank if you're not running a sale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>The old price, if this is on sale. Must be higher than the price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>The barcode on the item. The single most useful column you can fill in -- a barcode matches your product to our catalogue instantly and exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Who makes it, e.g. Coca-Cola. Helps us match your products correctly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pack_quantity</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>The size of one item, e.g. 2 for a 2L bottle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pack_unit</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>The measure for pack_quantity: L, ml, kg or g.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>image_1</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Optional. The exact filename of the main photo inside your images ZIP, e.g. "coke500.jpg".</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Filename of a photo inside your images ZIP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>image_2</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Optional. A second photo filename.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Filename of a photo inside your images ZIP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>image_3</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Optional. A third photo filename.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Filename of a photo inside your images ZIP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>image_4</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Optional. A fourth photo filename.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Filename of a photo inside your images ZIP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>image_5</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Optional. A fifth photo filename.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Images</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>If you're including photos, put them all in one ZIP file (no folders needed) and upload it alongside this spreadsheet. Each image_1 to image_5 value must exactly match a filename inside that ZIP, including the file extension (.jpg, .jpeg, .png, or .webp). Products without any image columns filled in will publish without a photo -- that's fine, you can add photos later.</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Filename of a photo inside your images ZIP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>The barcode column is the most useful one you can fill in. A barcode matches your product to the TRU Connect catalogue exactly, so businesses can compare it against other suppliers. Everything else is matched on the words you type.</t>
         </is>
       </c>
     </row>
@@ -947,130 +1058,131 @@
   <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="53" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Valid category names</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Type one of these exactly into the category column.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Food &amp; Grocery</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Beverages</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Snacks &amp; Confectionery</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Bakery</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Dairy &amp; Chilled</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Fresh Produce</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Meat &amp; Frozen</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Household &amp; Cleaning</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Personal Care</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Baby &amp; Family</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Stationery &amp; School</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Hardware &amp; General</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Electronics &amp; Accessories</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Packaging &amp; Disposable</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Clothing &amp; Apparel</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -1090,102 +1202,103 @@
   <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Valid unit names</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Type one of these exactly into the unit column ("Sold as").</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Each</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Pack</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Box</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Bag</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Bottle</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Can</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Dozen</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ml</t>
         </is>

--- a/frontend/mobile/assets/bulk-import/TRU_Connect_Product_Import_Template.xlsx
+++ b/frontend/mobile/assets/bulk-import/TRU_Connect_Product_Import_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Categories" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Units" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
